--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Daily Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,9 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -448,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -520,6 +521,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>50.679</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>-56</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -544,6 +544,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>44.538</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>-62</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-6</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -567,6 +567,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>38.875</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-68</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-6</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -590,6 +590,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>34.301</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>-73</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>-5</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -613,6 +613,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>31.634</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>-76</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -636,6 +636,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>34.301</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-73</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -659,6 +659,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>46192</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>-80</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>-7</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -682,6 +682,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>26.682</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>-82</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -705,6 +705,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>26.682</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-82</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -728,6 +728,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>23.727</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>-86</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -751,6 +751,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>23.727</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-86</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -774,6 +774,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-80</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -797,6 +797,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>26.682</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>-82</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -820,6 +820,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>46200</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>25.921</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>-83</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -843,6 +843,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>29.075</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-79</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -866,6 +866,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>-80</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -889,6 +889,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>25.921</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-83</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -912,6 +912,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>25.921</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-83</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -935,6 +935,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>25.175</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>-84</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -958,6 +958,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>26.682</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-82</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -981,6 +981,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>25.921</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-83</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1004,6 +1004,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>46208</v>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>23.024</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>-87</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1027,6 +1027,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>24.444</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>-85</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1050,6 +1050,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>-80</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1073,6 +1073,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>-80</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1096,6 +1096,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>29.915</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>-78</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1119,6 +1119,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>29.075</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>-79</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1142,6 +1142,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>-80</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1165,6 +1165,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>-80</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1188,6 +1188,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>25.921</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>-83</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1211,6 +1211,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>-80</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1234,6 +1234,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>29.075</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>-79</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1257,6 +1257,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>19.714</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>-92</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>-13</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1280,6 +1280,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>-80</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1303,6 +1303,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>46221</v>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>6.112</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>-124</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>-44</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1326,6 +1326,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>5.279</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>-127</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1349,6 +1349,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>6.365</v>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>-123</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1372,6 +1372,27 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B40" s="5" t="n"/>
+      <c r="C40" s="5" t="n">
+        <v>-122</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1393,6 +1393,23 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B41" s="5" t="n"/>
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="5" t="n"/>
+      <c r="E41" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1410,6 +1410,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>20.797</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>-123</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1433,6 +1433,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>19.565</v>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>-125</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1456,6 +1456,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>46228</v>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>19.565</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>-125</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1479,6 +1479,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="4" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>20.173</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>-124</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1502,6 +1502,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>18.974</v>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>-126</v>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1525,6 +1525,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>-127</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1548,6 +1548,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>-130</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1571,6 +1571,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>15.852</v>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>-132</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1594,6 +1594,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>14.994</v>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>-134</v>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1617,6 +1617,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>-135</v>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1640,6 +1640,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>14.23</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>-136</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1663,6 +1663,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>14.23</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>-136</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1686,6 +1686,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>13.269</v>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>-139</v>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1709,6 +1709,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>-140</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1732,6 +1732,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>-140</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1755,6 +1755,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>13.564</v>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>-138</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1778,6 +1778,27 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>46242</v>
+      </c>
+      <c r="B58" s="5" t="n"/>
+      <c r="C58" s="5" t="n">
+        <v>-143</v>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>-5</v>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1799,6 +1799,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>14.994</v>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>-134</v>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1822,6 +1822,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>15.412</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>-133</v>
+      </c>
+      <c r="D60" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1845,6 +1845,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>11.416</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>-144</v>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>-11</v>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1868,6 +1868,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>-145</v>
+      </c>
+      <c r="D62" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1891,6 +1891,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>11.416</v>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>-144</v>
+      </c>
+      <c r="D63" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1914,6 +1914,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>46249</v>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>12.069</v>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>-142</v>
+      </c>
+      <c r="D64" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1937,6 +1937,23 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B65" s="5" t="n"/>
+      <c r="C65" s="5" t="n"/>
+      <c r="D65" s="5" t="n"/>
+      <c r="E65" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1954,6 +1954,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="C66" s="5" t="n">
+        <v>-145</v>
+      </c>
+      <c r="D66" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1977,6 +1977,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>-145</v>
+      </c>
+      <c r="D67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2000,6 +2000,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="C68" s="5" t="n">
+        <v>-145</v>
+      </c>
+      <c r="D68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2023,6 +2023,23 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B69" s="5" t="n"/>
+      <c r="C69" s="5" t="n"/>
+      <c r="D69" s="5" t="n"/>
+      <c r="E69" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2040,6 +2040,23 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>46256</v>
+      </c>
+      <c r="B70" s="5" t="n"/>
+      <c r="C70" s="5" t="n"/>
+      <c r="D70" s="5" t="n"/>
+      <c r="E70" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2057,6 +2057,23 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B71" s="5" t="n"/>
+      <c r="C71" s="5" t="n"/>
+      <c r="D71" s="5" t="n"/>
+      <c r="E71" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2074,6 +2074,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>15.412</v>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>-133</v>
+      </c>
+      <c r="D72" s="5" t="n">
+        <v>-12</v>
+      </c>
+      <c r="E72" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2097,6 +2097,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="4" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>16.315</v>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>-131</v>
+      </c>
+      <c r="D73" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2120,6 +2120,29 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>-130</v>
+      </c>
+      <c r="D74" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2143,6 +2143,23 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="4" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B75" s="5" t="n"/>
+      <c r="C75" s="5" t="n"/>
+      <c r="D75" s="5" t="n"/>
+      <c r="E75" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2160,6 +2160,23 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="4" t="n">
+        <v>46264</v>
+      </c>
+      <c r="B76" s="5" t="n"/>
+      <c r="C76" s="5" t="n"/>
+      <c r="D76" s="5" t="n"/>
+      <c r="E76" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2177,6 +2177,23 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="4" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B77" s="5" t="n"/>
+      <c r="C77" s="5" t="n"/>
+      <c r="D77" s="5" t="n"/>
+      <c r="E77" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2194,6 +2194,23 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="4" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B78" s="5" t="n"/>
+      <c r="C78" s="5" t="n"/>
+      <c r="D78" s="5" t="n"/>
+      <c r="E78" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2211,6 +2211,23 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="4" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B79" s="5" t="n"/>
+      <c r="C79" s="5" t="n"/>
+      <c r="D79" s="5" t="n"/>
+      <c r="E79" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2228,6 +2228,23 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" s="4" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B80" s="5" t="n"/>
+      <c r="C80" s="5" t="n"/>
+      <c r="D80" s="5" t="n"/>
+      <c r="E80" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2245,23 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" s="4" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B81" s="5" t="n"/>
+      <c r="C81" s="5" t="n"/>
+      <c r="D81" s="5" t="n"/>
+      <c r="E81" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2262,6 +2262,23 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="4" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B82" s="5" t="n"/>
+      <c r="C82" s="5" t="n"/>
+      <c r="D82" s="5" t="n"/>
+      <c r="E82" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2279,6 +2279,23 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" s="4" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B83" s="5" t="n"/>
+      <c r="C83" s="5" t="n"/>
+      <c r="D83" s="5" t="n"/>
+      <c r="E83" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2296,6 +2296,23 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="4" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B84" s="5" t="n"/>
+      <c r="C84" s="5" t="n"/>
+      <c r="D84" s="5" t="n"/>
+      <c r="E84" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2313,6 +2313,23 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" s="4" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B85" s="5" t="n"/>
+      <c r="C85" s="5" t="n"/>
+      <c r="D85" s="5" t="n"/>
+      <c r="E85" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2330,6 +2330,23 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="4" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B86" s="5" t="n"/>
+      <c r="C86" s="5" t="n"/>
+      <c r="D86" s="5" t="n"/>
+      <c r="E86" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2347,6 +2347,23 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="4" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B87" s="5" t="n"/>
+      <c r="C87" s="5" t="n"/>
+      <c r="D87" s="5" t="n"/>
+      <c r="E87" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STRYMON_MARINO_POLE_SCRAPER.xlsx
+++ b/STRYMON_MARINO_POLE_SCRAPER.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2364,6 +2364,23 @@
         <v>658.85</v>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" s="4" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B88" s="5" t="n"/>
+      <c r="C88" s="5" t="n"/>
+      <c r="D88" s="5" t="n"/>
+      <c r="E88" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>63.641</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>658.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
